--- a/outputs/batch/loan_batch_2025-04-11_14-27-40/batch_analysis/combined_results.xlsx
+++ b/outputs/batch/loan_batch_2025-04-11_14-27-40/batch_analysis/combined_results.xlsx
@@ -66573,7 +66573,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -66582,31 +66582,31 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6806</v>
+        <v>0.5694</v>
       </c>
       <c r="E3" t="n">
         <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6806</v>
+        <v>0.5694</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6398</v>
+        <v>0.5802</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6806</v>
+        <v>0.5694</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6431</v>
+        <v>0.5744</v>
       </c>
       <c r="L3" t="n">
         <v/>
@@ -66615,7 +66615,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LogisticRegression</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -66624,31 +66624,31 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6667</v>
+        <v>0.5694</v>
       </c>
       <c r="E4" t="n">
         <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6667</v>
+        <v>0.5694</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6093</v>
+        <v>0.5802</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6667</v>
+        <v>0.5694</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6159</v>
+        <v>0.5744</v>
       </c>
       <c r="L4" t="n">
         <v/>
@@ -66657,40 +66657,40 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Accuracy</t>
+          <t>F1</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6389</v>
+        <v>0.5744</v>
       </c>
       <c r="E5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G5" t="n">
         <v>0.1</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6389</v>
+        <v>0.5694</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6389</v>
+        <v>0.5802</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6389</v>
+        <v>0.5694</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6389</v>
+        <v>0.5744</v>
       </c>
       <c r="L5" t="n">
         <v/>
@@ -66699,40 +66699,40 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SVM</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Accuracy</t>
+          <t>F1</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6944</v>
+        <v>0.5744</v>
       </c>
       <c r="E6" t="n">
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6944</v>
+        <v>0.5694</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4823</v>
+        <v>0.5802</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6944</v>
+        <v>0.5694</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5692</v>
+        <v>0.5744</v>
       </c>
       <c r="L6" t="n">
         <v/>
@@ -66746,23 +66746,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Accuracy</t>
+          <t>F1</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5694</v>
+        <v>0.5744</v>
       </c>
       <c r="E7" t="n">
         <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="H7" t="n">
         <v>0.5694</v>
@@ -66783,40 +66783,40 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Accuracy</t>
+          <t>Precision</t>
         </is>
       </c>
       <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.5881999999999999</v>
+      </c>
+      <c r="E8" t="n">
         <v>2</v>
       </c>
-      <c r="D8" t="n">
-        <v>0.6806</v>
-      </c>
-      <c r="E8" t="n">
-        <v>10</v>
-      </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G8" t="n">
         <v>0.1</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6806</v>
+        <v>0.5208</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6398</v>
+        <v>0.5881999999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6806</v>
+        <v>0.5208</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6431</v>
+        <v>0.5396</v>
       </c>
       <c r="L8" t="n">
         <v/>
@@ -66825,40 +66825,40 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LogisticRegression</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Accuracy</t>
+          <t>Precision</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6667</v>
+        <v>0.5869</v>
       </c>
       <c r="E9" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G9" t="n">
         <v>0.01</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6667</v>
+        <v>0.5278</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6093</v>
+        <v>0.5869</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6667</v>
+        <v>0.5278</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6159</v>
+        <v>0.5458</v>
       </c>
       <c r="L9" t="n">
         <v/>
@@ -66867,40 +66867,40 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Accuracy</t>
+          <t>Precision</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6319</v>
+        <v>0.5869</v>
       </c>
       <c r="E10" t="n">
         <v>5</v>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1</v>
+        <v>0.01</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6319</v>
+        <v>0.5278</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6296</v>
+        <v>0.5869</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6319</v>
+        <v>0.5278</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6307</v>
+        <v>0.5458</v>
       </c>
       <c r="L10" t="n">
         <v/>
@@ -66909,40 +66909,40 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SVM</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Accuracy</t>
+          <t>Recall</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6944</v>
+        <v>0.5694</v>
       </c>
       <c r="E11" t="n">
         <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G11" t="n">
         <v>0.1</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6944</v>
+        <v>0.5694</v>
       </c>
       <c r="I11" t="n">
-        <v>0.4823</v>
+        <v>0.5802</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6944</v>
+        <v>0.5694</v>
       </c>
       <c r="K11" t="n">
-        <v>0.5692</v>
+        <v>0.5744</v>
       </c>
       <c r="L11" t="n">
         <v/>
@@ -66956,11 +66956,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Accuracy</t>
+          <t>Recall</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D12" t="n">
         <v>0.5694</v>
@@ -66969,10 +66969,10 @@
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="H12" t="n">
         <v>0.5694</v>
@@ -66993,40 +66993,40 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Accuracy</t>
+          <t>Recall</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6806</v>
+        <v>0.5694</v>
       </c>
       <c r="E13" t="n">
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G13" t="n">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="H13" t="n">
-        <v>0.6806</v>
+        <v>0.5694</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6398</v>
+        <v>0.5802</v>
       </c>
       <c r="J13" t="n">
-        <v>0.6806</v>
+        <v>0.5694</v>
       </c>
       <c r="K13" t="n">
-        <v>0.6431</v>
+        <v>0.5744</v>
       </c>
       <c r="L13" t="n">
         <v/>
@@ -67035,7 +67035,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LogisticRegression</t>
+          <t>KNN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -67044,31 +67044,31 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6667</v>
+        <v>0.6806</v>
       </c>
       <c r="E14" t="n">
         <v>10</v>
       </c>
       <c r="F14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G14" t="n">
         <v>0.01</v>
       </c>
       <c r="H14" t="n">
-        <v>0.6667</v>
+        <v>0.6806</v>
       </c>
       <c r="I14" t="n">
-        <v>0.6093</v>
+        <v>0.6398</v>
       </c>
       <c r="J14" t="n">
-        <v>0.6667</v>
+        <v>0.6806</v>
       </c>
       <c r="K14" t="n">
-        <v>0.6159</v>
+        <v>0.6431</v>
       </c>
       <c r="L14" t="n">
         <v/>
@@ -67077,7 +67077,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>KNN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -67086,31 +67086,31 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>0.625</v>
+        <v>0.6806</v>
       </c>
       <c r="E15" t="n">
+        <v>10</v>
+      </c>
+      <c r="F15" t="n">
         <v>2</v>
       </c>
-      <c r="F15" t="n">
-        <v>3</v>
-      </c>
       <c r="G15" t="n">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="H15" t="n">
-        <v>0.625</v>
+        <v>0.6806</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6298</v>
+        <v>0.6398</v>
       </c>
       <c r="J15" t="n">
-        <v>0.625</v>
+        <v>0.6806</v>
       </c>
       <c r="K15" t="n">
-        <v>0.6273</v>
+        <v>0.6431</v>
       </c>
       <c r="L15" t="n">
         <v/>
@@ -67119,7 +67119,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SVM</t>
+          <t>KNN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -67131,7 +67131,7 @@
         <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6944</v>
+        <v>0.6806</v>
       </c>
       <c r="E16" t="n">
         <v>10</v>
@@ -67143,16 +67143,16 @@
         <v>0.01</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6944</v>
+        <v>0.6806</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4823</v>
+        <v>0.6398</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6944</v>
+        <v>0.6806</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5692</v>
+        <v>0.6431</v>
       </c>
       <c r="L16" t="n">
         <v/>
@@ -67161,7 +67161,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DecisionTree</t>
+          <t>KNN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -67173,28 +67173,28 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5744</v>
+        <v>0.6431</v>
       </c>
       <c r="E17" t="n">
         <v>10</v>
       </c>
       <c r="F17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1</v>
+        <v>0.01</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5694</v>
+        <v>0.6806</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5802</v>
+        <v>0.6398</v>
       </c>
       <c r="J17" t="n">
-        <v>0.5694</v>
+        <v>0.6806</v>
       </c>
       <c r="K17" t="n">
-        <v>0.5744</v>
+        <v>0.6431</v>
       </c>
       <c r="L17" t="n">
         <v/>
@@ -67212,7 +67212,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
         <v>0.6431</v>
@@ -67224,7 +67224,7 @@
         <v>2</v>
       </c>
       <c r="G18" t="n">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="H18" t="n">
         <v>0.6806</v>
@@ -67245,7 +67245,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>LogisticRegression</t>
+          <t>KNN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -67254,31 +67254,31 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6159</v>
+        <v>0.6431</v>
       </c>
       <c r="E19" t="n">
         <v>10</v>
       </c>
       <c r="F19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G19" t="n">
         <v>0.01</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6667</v>
+        <v>0.6806</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6093</v>
+        <v>0.6398</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6667</v>
+        <v>0.6806</v>
       </c>
       <c r="K19" t="n">
-        <v>0.6159</v>
+        <v>0.6431</v>
       </c>
       <c r="L19" t="n">
         <v/>
@@ -67287,40 +67287,40 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>KNN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>Precision</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.6389</v>
+        <v>0.6398</v>
       </c>
       <c r="E20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1</v>
+        <v>0.01</v>
       </c>
       <c r="H20" t="n">
-        <v>0.6389</v>
+        <v>0.6806</v>
       </c>
       <c r="I20" t="n">
-        <v>0.6389</v>
+        <v>0.6398</v>
       </c>
       <c r="J20" t="n">
-        <v>0.6389</v>
+        <v>0.6806</v>
       </c>
       <c r="K20" t="n">
-        <v>0.6389</v>
+        <v>0.6431</v>
       </c>
       <c r="L20" t="n">
         <v/>
@@ -67329,19 +67329,19 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SVM</t>
+          <t>KNN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>Precision</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D21" t="n">
-        <v>0.5692</v>
+        <v>0.6398</v>
       </c>
       <c r="E21" t="n">
         <v>10</v>
@@ -67350,19 +67350,19 @@
         <v>2</v>
       </c>
       <c r="G21" t="n">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="H21" t="n">
-        <v>0.6944</v>
+        <v>0.6806</v>
       </c>
       <c r="I21" t="n">
-        <v>0.4823</v>
+        <v>0.6398</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6944</v>
+        <v>0.6806</v>
       </c>
       <c r="K21" t="n">
-        <v>0.5692</v>
+        <v>0.6431</v>
       </c>
       <c r="L21" t="n">
         <v/>
@@ -67371,40 +67371,40 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>DecisionTree</t>
+          <t>KNN</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>Precision</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5744</v>
+        <v>0.6398</v>
       </c>
       <c r="E22" t="n">
         <v>10</v>
       </c>
       <c r="F22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G22" t="n">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="H22" t="n">
-        <v>0.5694</v>
+        <v>0.6806</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5802</v>
+        <v>0.6398</v>
       </c>
       <c r="J22" t="n">
-        <v>0.5694</v>
+        <v>0.6806</v>
       </c>
       <c r="K22" t="n">
-        <v>0.5744</v>
+        <v>0.6431</v>
       </c>
       <c r="L22" t="n">
         <v/>
@@ -67418,14 +67418,14 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>Recall</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.6431</v>
+        <v>0.6806</v>
       </c>
       <c r="E23" t="n">
         <v>10</v>
@@ -67434,7 +67434,7 @@
         <v>2</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1</v>
+        <v>0.01</v>
       </c>
       <c r="H23" t="n">
         <v>0.6806</v>
@@ -67455,40 +67455,40 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>LogisticRegression</t>
+          <t>KNN</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>Recall</t>
         </is>
       </c>
       <c r="C24" t="n">
         <v>2</v>
       </c>
       <c r="D24" t="n">
-        <v>0.6159</v>
+        <v>0.6806</v>
       </c>
       <c r="E24" t="n">
         <v>10</v>
       </c>
       <c r="F24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G24" t="n">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="H24" t="n">
-        <v>0.6667</v>
+        <v>0.6806</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6093</v>
+        <v>0.6398</v>
       </c>
       <c r="J24" t="n">
-        <v>0.6667</v>
+        <v>0.6806</v>
       </c>
       <c r="K24" t="n">
-        <v>0.6159</v>
+        <v>0.6431</v>
       </c>
       <c r="L24" t="n">
         <v/>
@@ -67497,40 +67497,40 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>KNN</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>Recall</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D25" t="n">
-        <v>0.6307</v>
+        <v>0.6806</v>
       </c>
       <c r="E25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1</v>
+        <v>0.01</v>
       </c>
       <c r="H25" t="n">
-        <v>0.6319</v>
+        <v>0.6806</v>
       </c>
       <c r="I25" t="n">
-        <v>0.6296</v>
+        <v>0.6398</v>
       </c>
       <c r="J25" t="n">
-        <v>0.6319</v>
+        <v>0.6806</v>
       </c>
       <c r="K25" t="n">
-        <v>0.6307</v>
+        <v>0.6431</v>
       </c>
       <c r="L25" t="n">
         <v/>
@@ -67539,19 +67539,19 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SVM</t>
+          <t>LogisticRegression</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>Accuracy</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>0.5692</v>
+        <v>0.6667</v>
       </c>
       <c r="E26" t="n">
         <v>10</v>
@@ -67560,19 +67560,19 @@
         <v>2</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1</v>
+        <v>0.01</v>
       </c>
       <c r="H26" t="n">
-        <v>0.6944</v>
+        <v>0.6667</v>
       </c>
       <c r="I26" t="n">
-        <v>0.4823</v>
+        <v>0.6093</v>
       </c>
       <c r="J26" t="n">
-        <v>0.6944</v>
+        <v>0.6667</v>
       </c>
       <c r="K26" t="n">
-        <v>0.5692</v>
+        <v>0.6159</v>
       </c>
       <c r="L26" t="n">
         <v/>
@@ -67581,40 +67581,40 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DecisionTree</t>
+          <t>LogisticRegression</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>Accuracy</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D27" t="n">
-        <v>0.5744</v>
+        <v>0.6667</v>
       </c>
       <c r="E27" t="n">
         <v>10</v>
       </c>
       <c r="F27" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G27" t="n">
-        <v>0.1</v>
+        <v>0.01</v>
       </c>
       <c r="H27" t="n">
-        <v>0.5694</v>
+        <v>0.6667</v>
       </c>
       <c r="I27" t="n">
-        <v>0.5802</v>
+        <v>0.6093</v>
       </c>
       <c r="J27" t="n">
-        <v>0.5694</v>
+        <v>0.6667</v>
       </c>
       <c r="K27" t="n">
-        <v>0.5744</v>
+        <v>0.6159</v>
       </c>
       <c r="L27" t="n">
         <v/>
@@ -67623,40 +67623,40 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>LogisticRegression</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>Accuracy</t>
         </is>
       </c>
       <c r="C28" t="n">
         <v>3</v>
       </c>
       <c r="D28" t="n">
-        <v>0.6431</v>
+        <v>0.6667</v>
       </c>
       <c r="E28" t="n">
         <v>10</v>
       </c>
       <c r="F28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G28" t="n">
         <v>0.01</v>
       </c>
       <c r="H28" t="n">
-        <v>0.6806</v>
+        <v>0.6667</v>
       </c>
       <c r="I28" t="n">
-        <v>0.6398</v>
+        <v>0.6093</v>
       </c>
       <c r="J28" t="n">
-        <v>0.6806</v>
+        <v>0.6667</v>
       </c>
       <c r="K28" t="n">
-        <v>0.6431</v>
+        <v>0.6159</v>
       </c>
       <c r="L28" t="n">
         <v/>
@@ -67674,7 +67674,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D29" t="n">
         <v>0.6159</v>
@@ -67683,7 +67683,7 @@
         <v>10</v>
       </c>
       <c r="F29" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G29" t="n">
         <v>0.01</v>
@@ -67707,7 +67707,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>LogisticRegression</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -67716,31 +67716,31 @@
         </is>
       </c>
       <c r="C30" t="n">
+        <v>2</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.6159</v>
+      </c>
+      <c r="E30" t="n">
+        <v>10</v>
+      </c>
+      <c r="F30" t="n">
         <v>3</v>
       </c>
-      <c r="D30" t="n">
-        <v>0.6293</v>
-      </c>
-      <c r="E30" t="n">
-        <v>2</v>
-      </c>
-      <c r="F30" t="n">
-        <v>5</v>
-      </c>
       <c r="G30" t="n">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="H30" t="n">
-        <v>0.625</v>
+        <v>0.6667</v>
       </c>
       <c r="I30" t="n">
-        <v>0.6345</v>
+        <v>0.6093</v>
       </c>
       <c r="J30" t="n">
-        <v>0.625</v>
+        <v>0.6667</v>
       </c>
       <c r="K30" t="n">
-        <v>0.6293</v>
+        <v>0.6159</v>
       </c>
       <c r="L30" t="n">
         <v/>
@@ -67749,7 +67749,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SVM</t>
+          <t>LogisticRegression</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -67761,28 +67761,28 @@
         <v>3</v>
       </c>
       <c r="D31" t="n">
-        <v>0.5692</v>
+        <v>0.6159</v>
       </c>
       <c r="E31" t="n">
         <v>10</v>
       </c>
       <c r="F31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G31" t="n">
         <v>0.01</v>
       </c>
       <c r="H31" t="n">
-        <v>0.6944</v>
+        <v>0.6667</v>
       </c>
       <c r="I31" t="n">
-        <v>0.4823</v>
+        <v>0.6093</v>
       </c>
       <c r="J31" t="n">
-        <v>0.6944</v>
+        <v>0.6667</v>
       </c>
       <c r="K31" t="n">
-        <v>0.5692</v>
+        <v>0.6159</v>
       </c>
       <c r="L31" t="n">
         <v/>
@@ -67791,7 +67791,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>DecisionTree</t>
+          <t>LogisticRegression</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -67803,28 +67803,28 @@
         <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>0.5881999999999999</v>
+        <v>0.6093</v>
       </c>
       <c r="E32" t="n">
+        <v>10</v>
+      </c>
+      <c r="F32" t="n">
         <v>2</v>
       </c>
-      <c r="F32" t="n">
-        <v>5</v>
-      </c>
       <c r="G32" t="n">
-        <v>0.1</v>
+        <v>0.01</v>
       </c>
       <c r="H32" t="n">
-        <v>0.5208</v>
+        <v>0.6667</v>
       </c>
       <c r="I32" t="n">
-        <v>0.5881999999999999</v>
+        <v>0.6093</v>
       </c>
       <c r="J32" t="n">
-        <v>0.5208</v>
+        <v>0.6667</v>
       </c>
       <c r="K32" t="n">
-        <v>0.5396</v>
+        <v>0.6159</v>
       </c>
       <c r="L32" t="n">
         <v/>
@@ -67833,7 +67833,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>LogisticRegression</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -67842,31 +67842,31 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D33" t="n">
-        <v>0.6398</v>
+        <v>0.6093</v>
       </c>
       <c r="E33" t="n">
         <v>10</v>
       </c>
       <c r="F33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G33" t="n">
         <v>0.01</v>
       </c>
       <c r="H33" t="n">
-        <v>0.6806</v>
+        <v>0.6667</v>
       </c>
       <c r="I33" t="n">
-        <v>0.6398</v>
+        <v>0.6093</v>
       </c>
       <c r="J33" t="n">
-        <v>0.6806</v>
+        <v>0.6667</v>
       </c>
       <c r="K33" t="n">
-        <v>0.6431</v>
+        <v>0.6159</v>
       </c>
       <c r="L33" t="n">
         <v/>
@@ -67884,7 +67884,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D34" t="n">
         <v>0.6093</v>
@@ -67893,7 +67893,7 @@
         <v>10</v>
       </c>
       <c r="F34" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G34" t="n">
         <v>0.01</v>
@@ -67917,40 +67917,40 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>LogisticRegression</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Precision</t>
+          <t>Recall</t>
         </is>
       </c>
       <c r="C35" t="n">
         <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>0.6389</v>
+        <v>0.6667</v>
       </c>
       <c r="E35" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F35" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G35" t="n">
-        <v>0.1</v>
+        <v>0.01</v>
       </c>
       <c r="H35" t="n">
-        <v>0.6389</v>
+        <v>0.6667</v>
       </c>
       <c r="I35" t="n">
-        <v>0.6389</v>
+        <v>0.6093</v>
       </c>
       <c r="J35" t="n">
-        <v>0.6389</v>
+        <v>0.6667</v>
       </c>
       <c r="K35" t="n">
-        <v>0.6389</v>
+        <v>0.6159</v>
       </c>
       <c r="L35" t="n">
         <v/>
@@ -67959,40 +67959,40 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SVM</t>
+          <t>LogisticRegression</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Precision</t>
+          <t>Recall</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D36" t="n">
-        <v>0.4823</v>
+        <v>0.6667</v>
       </c>
       <c r="E36" t="n">
         <v>10</v>
       </c>
       <c r="F36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G36" t="n">
         <v>0.01</v>
       </c>
       <c r="H36" t="n">
-        <v>0.6944</v>
+        <v>0.6667</v>
       </c>
       <c r="I36" t="n">
-        <v>0.4823</v>
+        <v>0.6093</v>
       </c>
       <c r="J36" t="n">
-        <v>0.6944</v>
+        <v>0.6667</v>
       </c>
       <c r="K36" t="n">
-        <v>0.5692</v>
+        <v>0.6159</v>
       </c>
       <c r="L36" t="n">
         <v/>
@@ -68001,40 +68001,40 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>DecisionTree</t>
+          <t>LogisticRegression</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Precision</t>
+          <t>Recall</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D37" t="n">
-        <v>0.5869</v>
+        <v>0.6667</v>
       </c>
       <c r="E37" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F37" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G37" t="n">
         <v>0.01</v>
       </c>
       <c r="H37" t="n">
-        <v>0.5278</v>
+        <v>0.6667</v>
       </c>
       <c r="I37" t="n">
-        <v>0.5869</v>
+        <v>0.6093</v>
       </c>
       <c r="J37" t="n">
-        <v>0.5278</v>
+        <v>0.6667</v>
       </c>
       <c r="K37" t="n">
-        <v>0.5458</v>
+        <v>0.6159</v>
       </c>
       <c r="L37" t="n">
         <v/>
@@ -68043,40 +68043,40 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Precision</t>
+          <t>Accuracy</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D38" t="n">
-        <v>0.6398</v>
+        <v>0.6389</v>
       </c>
       <c r="E38" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F38" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G38" t="n">
         <v>0.1</v>
       </c>
       <c r="H38" t="n">
-        <v>0.6806</v>
+        <v>0.6389</v>
       </c>
       <c r="I38" t="n">
-        <v>0.6398</v>
+        <v>0.6389</v>
       </c>
       <c r="J38" t="n">
-        <v>0.6806</v>
+        <v>0.6389</v>
       </c>
       <c r="K38" t="n">
-        <v>0.6431</v>
+        <v>0.6389</v>
       </c>
       <c r="L38" t="n">
         <v/>
@@ -68085,40 +68085,40 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>LogisticRegression</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Precision</t>
+          <t>Accuracy</t>
         </is>
       </c>
       <c r="C39" t="n">
         <v>2</v>
       </c>
       <c r="D39" t="n">
-        <v>0.6093</v>
+        <v>0.6319</v>
       </c>
       <c r="E39" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G39" t="n">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="H39" t="n">
-        <v>0.6667</v>
+        <v>0.6319</v>
       </c>
       <c r="I39" t="n">
-        <v>0.6093</v>
+        <v>0.6296</v>
       </c>
       <c r="J39" t="n">
-        <v>0.6667</v>
+        <v>0.6319</v>
       </c>
       <c r="K39" t="n">
-        <v>0.6159</v>
+        <v>0.6307</v>
       </c>
       <c r="L39" t="n">
         <v/>
@@ -68132,35 +68132,35 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Precision</t>
+          <t>Accuracy</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D40" t="n">
-        <v>0.6345</v>
+        <v>0.625</v>
       </c>
       <c r="E40" t="n">
         <v>2</v>
       </c>
       <c r="F40" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G40" t="n">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="H40" t="n">
         <v>0.625</v>
       </c>
       <c r="I40" t="n">
-        <v>0.6345</v>
+        <v>0.6298</v>
       </c>
       <c r="J40" t="n">
         <v>0.625</v>
       </c>
       <c r="K40" t="n">
-        <v>0.6293</v>
+        <v>0.6273</v>
       </c>
       <c r="L40" t="n">
         <v/>
@@ -68169,40 +68169,40 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SVM</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Precision</t>
+          <t>F1</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D41" t="n">
-        <v>0.4823</v>
+        <v>0.6389</v>
       </c>
       <c r="E41" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F41" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G41" t="n">
         <v>0.1</v>
       </c>
       <c r="H41" t="n">
-        <v>0.6944</v>
+        <v>0.6389</v>
       </c>
       <c r="I41" t="n">
-        <v>0.4823</v>
+        <v>0.6389</v>
       </c>
       <c r="J41" t="n">
-        <v>0.6944</v>
+        <v>0.6389</v>
       </c>
       <c r="K41" t="n">
-        <v>0.5692</v>
+        <v>0.6389</v>
       </c>
       <c r="L41" t="n">
         <v/>
@@ -68211,40 +68211,40 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>DecisionTree</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Precision</t>
+          <t>F1</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D42" t="n">
-        <v>0.5869</v>
+        <v>0.6307</v>
       </c>
       <c r="E42" t="n">
         <v>5</v>
       </c>
       <c r="F42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G42" t="n">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="H42" t="n">
-        <v>0.5278</v>
+        <v>0.6319</v>
       </c>
       <c r="I42" t="n">
-        <v>0.5869</v>
+        <v>0.6296</v>
       </c>
       <c r="J42" t="n">
-        <v>0.5278</v>
+        <v>0.6319</v>
       </c>
       <c r="K42" t="n">
-        <v>0.5458</v>
+        <v>0.6307</v>
       </c>
       <c r="L42" t="n">
         <v/>
@@ -68253,40 +68253,40 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Precision</t>
+          <t>F1</t>
         </is>
       </c>
       <c r="C43" t="n">
         <v>3</v>
       </c>
       <c r="D43" t="n">
-        <v>0.6398</v>
+        <v>0.6293</v>
       </c>
       <c r="E43" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F43" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G43" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="H43" t="n">
-        <v>0.6806</v>
+        <v>0.625</v>
       </c>
       <c r="I43" t="n">
-        <v>0.6398</v>
+        <v>0.6345</v>
       </c>
       <c r="J43" t="n">
-        <v>0.6806</v>
+        <v>0.625</v>
       </c>
       <c r="K43" t="n">
-        <v>0.6431</v>
+        <v>0.6293</v>
       </c>
       <c r="L43" t="n">
         <v/>
@@ -68295,7 +68295,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>LogisticRegression</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -68304,31 +68304,31 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D44" t="n">
-        <v>0.6093</v>
+        <v>0.6389</v>
       </c>
       <c r="E44" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F44" t="n">
         <v>4</v>
       </c>
       <c r="G44" t="n">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="H44" t="n">
-        <v>0.6667</v>
+        <v>0.6389</v>
       </c>
       <c r="I44" t="n">
-        <v>0.6093</v>
+        <v>0.6389</v>
       </c>
       <c r="J44" t="n">
-        <v>0.6667</v>
+        <v>0.6389</v>
       </c>
       <c r="K44" t="n">
-        <v>0.6159</v>
+        <v>0.6389</v>
       </c>
       <c r="L44" t="n">
         <v/>
@@ -68346,7 +68346,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D45" t="n">
         <v>0.6345</v>
@@ -68358,7 +68358,7 @@
         <v>5</v>
       </c>
       <c r="G45" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="H45" t="n">
         <v>0.625</v>
@@ -68379,7 +68379,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SVM</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -68391,28 +68391,28 @@
         <v>3</v>
       </c>
       <c r="D46" t="n">
-        <v>0.4823</v>
+        <v>0.6345</v>
       </c>
       <c r="E46" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F46" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G46" t="n">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="H46" t="n">
-        <v>0.6944</v>
+        <v>0.625</v>
       </c>
       <c r="I46" t="n">
-        <v>0.4823</v>
+        <v>0.6345</v>
       </c>
       <c r="J46" t="n">
-        <v>0.6944</v>
+        <v>0.625</v>
       </c>
       <c r="K46" t="n">
-        <v>0.5692</v>
+        <v>0.6293</v>
       </c>
       <c r="L46" t="n">
         <v/>
@@ -68421,7 +68421,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>DecisionTree</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -68433,28 +68433,28 @@
         <v>1</v>
       </c>
       <c r="D47" t="n">
-        <v>0.5694</v>
+        <v>0.6389</v>
       </c>
       <c r="E47" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F47" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G47" t="n">
         <v>0.1</v>
       </c>
       <c r="H47" t="n">
-        <v>0.5694</v>
+        <v>0.6389</v>
       </c>
       <c r="I47" t="n">
-        <v>0.5802</v>
+        <v>0.6389</v>
       </c>
       <c r="J47" t="n">
-        <v>0.5694</v>
+        <v>0.6389</v>
       </c>
       <c r="K47" t="n">
-        <v>0.5744</v>
+        <v>0.6389</v>
       </c>
       <c r="L47" t="n">
         <v/>
@@ -68463,7 +68463,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -68472,31 +68472,31 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D48" t="n">
-        <v>0.6806</v>
+        <v>0.6319</v>
       </c>
       <c r="E48" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F48" t="n">
         <v>2</v>
       </c>
       <c r="G48" t="n">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="H48" t="n">
-        <v>0.6806</v>
+        <v>0.6319</v>
       </c>
       <c r="I48" t="n">
-        <v>0.6398</v>
+        <v>0.6296</v>
       </c>
       <c r="J48" t="n">
-        <v>0.6806</v>
+        <v>0.6319</v>
       </c>
       <c r="K48" t="n">
-        <v>0.6431</v>
+        <v>0.6307</v>
       </c>
       <c r="L48" t="n">
         <v/>
@@ -68505,7 +68505,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>LogisticRegression</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -68514,31 +68514,31 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D49" t="n">
-        <v>0.6667</v>
+        <v>0.625</v>
       </c>
       <c r="E49" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G49" t="n">
         <v>0.01</v>
       </c>
       <c r="H49" t="n">
-        <v>0.6667</v>
+        <v>0.625</v>
       </c>
       <c r="I49" t="n">
-        <v>0.6093</v>
+        <v>0.6298</v>
       </c>
       <c r="J49" t="n">
-        <v>0.6667</v>
+        <v>0.625</v>
       </c>
       <c r="K49" t="n">
-        <v>0.6159</v>
+        <v>0.6273</v>
       </c>
       <c r="L49" t="n">
         <v/>
@@ -68547,40 +68547,40 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>SVM</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Recall</t>
+          <t>Accuracy</t>
         </is>
       </c>
       <c r="C50" t="n">
         <v>1</v>
       </c>
       <c r="D50" t="n">
-        <v>0.6389</v>
+        <v>0.6944</v>
       </c>
       <c r="E50" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F50" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G50" t="n">
-        <v>0.1</v>
+        <v>0.01</v>
       </c>
       <c r="H50" t="n">
-        <v>0.6389</v>
+        <v>0.6944</v>
       </c>
       <c r="I50" t="n">
-        <v>0.6389</v>
+        <v>0.4823</v>
       </c>
       <c r="J50" t="n">
-        <v>0.6389</v>
+        <v>0.6944</v>
       </c>
       <c r="K50" t="n">
-        <v>0.6389</v>
+        <v>0.5692</v>
       </c>
       <c r="L50" t="n">
         <v/>
@@ -68594,11 +68594,11 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Recall</t>
+          <t>Accuracy</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D51" t="n">
         <v>0.6944</v>
@@ -68610,7 +68610,7 @@
         <v>2</v>
       </c>
       <c r="G51" t="n">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="H51" t="n">
         <v>0.6944</v>
@@ -68631,40 +68631,40 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>DecisionTree</t>
+          <t>SVM</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Recall</t>
+          <t>Accuracy</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D52" t="n">
-        <v>0.5694</v>
+        <v>0.6944</v>
       </c>
       <c r="E52" t="n">
         <v>10</v>
       </c>
       <c r="F52" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G52" t="n">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="H52" t="n">
-        <v>0.5694</v>
+        <v>0.6944</v>
       </c>
       <c r="I52" t="n">
-        <v>0.5802</v>
+        <v>0.4823</v>
       </c>
       <c r="J52" t="n">
-        <v>0.5694</v>
+        <v>0.6944</v>
       </c>
       <c r="K52" t="n">
-        <v>0.5744</v>
+        <v>0.5692</v>
       </c>
       <c r="L52" t="n">
         <v/>
@@ -68673,19 +68673,19 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>SVM</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Recall</t>
+          <t>F1</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D53" t="n">
-        <v>0.6806</v>
+        <v>0.5692</v>
       </c>
       <c r="E53" t="n">
         <v>10</v>
@@ -68694,19 +68694,19 @@
         <v>2</v>
       </c>
       <c r="G53" t="n">
-        <v>0.1</v>
+        <v>0.01</v>
       </c>
       <c r="H53" t="n">
-        <v>0.6806</v>
+        <v>0.6944</v>
       </c>
       <c r="I53" t="n">
-        <v>0.6398</v>
+        <v>0.4823</v>
       </c>
       <c r="J53" t="n">
-        <v>0.6806</v>
+        <v>0.6944</v>
       </c>
       <c r="K53" t="n">
-        <v>0.6431</v>
+        <v>0.5692</v>
       </c>
       <c r="L53" t="n">
         <v/>
@@ -68715,40 +68715,40 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>LogisticRegression</t>
+          <t>SVM</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Recall</t>
+          <t>F1</t>
         </is>
       </c>
       <c r="C54" t="n">
         <v>2</v>
       </c>
       <c r="D54" t="n">
-        <v>0.6667</v>
+        <v>0.5692</v>
       </c>
       <c r="E54" t="n">
         <v>10</v>
       </c>
       <c r="F54" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G54" t="n">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="H54" t="n">
-        <v>0.6667</v>
+        <v>0.6944</v>
       </c>
       <c r="I54" t="n">
-        <v>0.6093</v>
+        <v>0.4823</v>
       </c>
       <c r="J54" t="n">
-        <v>0.6667</v>
+        <v>0.6944</v>
       </c>
       <c r="K54" t="n">
-        <v>0.6159</v>
+        <v>0.5692</v>
       </c>
       <c r="L54" t="n">
         <v/>
@@ -68757,40 +68757,40 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>SVM</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Recall</t>
+          <t>F1</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D55" t="n">
-        <v>0.6319</v>
+        <v>0.5692</v>
       </c>
       <c r="E55" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G55" t="n">
-        <v>0.1</v>
+        <v>0.01</v>
       </c>
       <c r="H55" t="n">
-        <v>0.6319</v>
+        <v>0.6944</v>
       </c>
       <c r="I55" t="n">
-        <v>0.6296</v>
+        <v>0.4823</v>
       </c>
       <c r="J55" t="n">
-        <v>0.6319</v>
+        <v>0.6944</v>
       </c>
       <c r="K55" t="n">
-        <v>0.6307</v>
+        <v>0.5692</v>
       </c>
       <c r="L55" t="n">
         <v/>
@@ -68804,14 +68804,14 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Recall</t>
+          <t>Precision</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D56" t="n">
-        <v>0.6944</v>
+        <v>0.4823</v>
       </c>
       <c r="E56" t="n">
         <v>10</v>
@@ -68820,7 +68820,7 @@
         <v>2</v>
       </c>
       <c r="G56" t="n">
-        <v>0.1</v>
+        <v>0.01</v>
       </c>
       <c r="H56" t="n">
         <v>0.6944</v>
@@ -68841,40 +68841,40 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>DecisionTree</t>
+          <t>SVM</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Recall</t>
+          <t>Precision</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D57" t="n">
-        <v>0.5694</v>
+        <v>0.4823</v>
       </c>
       <c r="E57" t="n">
         <v>10</v>
       </c>
       <c r="F57" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G57" t="n">
         <v>0.1</v>
       </c>
       <c r="H57" t="n">
-        <v>0.5694</v>
+        <v>0.6944</v>
       </c>
       <c r="I57" t="n">
-        <v>0.5802</v>
+        <v>0.4823</v>
       </c>
       <c r="J57" t="n">
-        <v>0.5694</v>
+        <v>0.6944</v>
       </c>
       <c r="K57" t="n">
-        <v>0.5744</v>
+        <v>0.5692</v>
       </c>
       <c r="L57" t="n">
         <v/>
@@ -68883,19 +68883,19 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>SVM</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Recall</t>
+          <t>Precision</t>
         </is>
       </c>
       <c r="C58" t="n">
         <v>3</v>
       </c>
       <c r="D58" t="n">
-        <v>0.6806</v>
+        <v>0.4823</v>
       </c>
       <c r="E58" t="n">
         <v>10</v>
@@ -68907,16 +68907,16 @@
         <v>0.01</v>
       </c>
       <c r="H58" t="n">
-        <v>0.6806</v>
+        <v>0.6944</v>
       </c>
       <c r="I58" t="n">
-        <v>0.6398</v>
+        <v>0.4823</v>
       </c>
       <c r="J58" t="n">
-        <v>0.6806</v>
+        <v>0.6944</v>
       </c>
       <c r="K58" t="n">
-        <v>0.6431</v>
+        <v>0.5692</v>
       </c>
       <c r="L58" t="n">
         <v/>
@@ -68925,7 +68925,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>LogisticRegression</t>
+          <t>SVM</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -68934,31 +68934,31 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D59" t="n">
-        <v>0.6667</v>
+        <v>0.6944</v>
       </c>
       <c r="E59" t="n">
         <v>10</v>
       </c>
       <c r="F59" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G59" t="n">
         <v>0.01</v>
       </c>
       <c r="H59" t="n">
-        <v>0.6667</v>
+        <v>0.6944</v>
       </c>
       <c r="I59" t="n">
-        <v>0.6093</v>
+        <v>0.4823</v>
       </c>
       <c r="J59" t="n">
-        <v>0.6667</v>
+        <v>0.6944</v>
       </c>
       <c r="K59" t="n">
-        <v>0.6159</v>
+        <v>0.5692</v>
       </c>
       <c r="L59" t="n">
         <v/>
@@ -68967,7 +68967,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>SVM</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -68976,31 +68976,31 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D60" t="n">
-        <v>0.625</v>
+        <v>0.6944</v>
       </c>
       <c r="E60" t="n">
+        <v>10</v>
+      </c>
+      <c r="F60" t="n">
         <v>2</v>
       </c>
-      <c r="F60" t="n">
-        <v>3</v>
-      </c>
       <c r="G60" t="n">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="H60" t="n">
-        <v>0.625</v>
+        <v>0.6944</v>
       </c>
       <c r="I60" t="n">
-        <v>0.6298</v>
+        <v>0.4823</v>
       </c>
       <c r="J60" t="n">
-        <v>0.625</v>
+        <v>0.6944</v>
       </c>
       <c r="K60" t="n">
-        <v>0.6273</v>
+        <v>0.5692</v>
       </c>
       <c r="L60" t="n">
         <v/>
@@ -69185,12 +69185,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TVAE</t>
+          <t>GaussianCopula</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -69199,28 +69199,28 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6944</v>
+        <v>0.7292</v>
       </c>
       <c r="F3" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="G3" t="n">
-        <v>614</v>
+        <v>10000</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6944</v>
+        <v>0.7292</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4823</v>
+        <v>0.7309</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6944</v>
+        <v>0.7292</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5692</v>
+        <v>0.73</v>
       </c>
       <c r="L3" t="n">
         <v/>
@@ -69234,7 +69234,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LogisticRegression</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -69243,28 +69243,28 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7917</v>
+        <v>0.7292</v>
       </c>
       <c r="F4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="G4" t="n">
-        <v>614</v>
+        <v>10000</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7917</v>
+        <v>0.7292</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7856</v>
+        <v>0.7385</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7917</v>
+        <v>0.7292</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7871</v>
+        <v>0.733</v>
       </c>
       <c r="L4" t="n">
         <v/>
@@ -69278,19 +69278,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Accuracy</t>
+          <t>F1</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8194</v>
+        <v>0.7342</v>
       </c>
       <c r="F5" t="n">
         <v>50</v>
@@ -69299,16 +69299,16 @@
         <v>10000</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8194</v>
+        <v>0.7292</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8287</v>
+        <v>0.7427</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8194</v>
+        <v>0.7292</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8011</v>
+        <v>0.7342</v>
       </c>
       <c r="L5" t="n">
         <v/>
@@ -69317,42 +69317,42 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CTGAN</t>
+          <t>GaussianCopula</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SVM</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Accuracy</t>
+          <t>F1</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7014</v>
+        <v>0.733</v>
       </c>
       <c r="F6" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="G6" t="n">
-        <v>614</v>
+        <v>10000</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7014</v>
+        <v>0.7292</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7912</v>
+        <v>0.7385</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7014</v>
+        <v>0.7292</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5851</v>
+        <v>0.733</v>
       </c>
       <c r="L6" t="n">
         <v/>
@@ -69371,14 +69371,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Accuracy</t>
+          <t>F1</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7292</v>
+        <v>0.73</v>
       </c>
       <c r="F7" t="n">
         <v>50</v>
@@ -69405,42 +69405,42 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TVAE</t>
+          <t>GaussianCopula</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Accuracy</t>
+          <t>Precision</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6944</v>
+        <v>0.7427</v>
       </c>
       <c r="F8" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="G8" t="n">
-        <v>614</v>
+        <v>10000</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6944</v>
+        <v>0.7292</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4823</v>
+        <v>0.7427</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6944</v>
+        <v>0.7292</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5692</v>
+        <v>0.7342</v>
       </c>
       <c r="L8" t="n">
         <v/>
@@ -69454,37 +69454,37 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>LogisticRegression</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Accuracy</t>
+          <t>Precision</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7917</v>
+        <v>0.7385</v>
       </c>
       <c r="F9" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="G9" t="n">
-        <v>614</v>
+        <v>10000</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7917</v>
+        <v>0.7292</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7856</v>
+        <v>0.7385</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7917</v>
+        <v>0.7292</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7871</v>
+        <v>0.733</v>
       </c>
       <c r="L9" t="n">
         <v/>
@@ -69498,37 +69498,37 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Accuracy</t>
+          <t>Precision</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8056</v>
+        <v>0.7309</v>
       </c>
       <c r="F10" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="G10" t="n">
-        <v>614</v>
+        <v>10000</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8056</v>
+        <v>0.7292</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8058999999999999</v>
+        <v>0.7309</v>
       </c>
       <c r="J10" t="n">
-        <v>0.8056</v>
+        <v>0.7292</v>
       </c>
       <c r="K10" t="n">
-        <v>0.7886</v>
+        <v>0.73</v>
       </c>
       <c r="L10" t="n">
         <v/>
@@ -69537,42 +69537,42 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CTGAN</t>
+          <t>GaussianCopula</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SVM</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Accuracy</t>
+          <t>Recall</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>0.7014</v>
+        <v>0.7292</v>
       </c>
       <c r="F11" t="n">
         <v>50</v>
       </c>
       <c r="G11" t="n">
-        <v>1842</v>
+        <v>10000</v>
       </c>
       <c r="H11" t="n">
-        <v>0.7014</v>
+        <v>0.7292</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6913</v>
+        <v>0.7427</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7014</v>
+        <v>0.7292</v>
       </c>
       <c r="K11" t="n">
-        <v>0.5965</v>
+        <v>0.7342</v>
       </c>
       <c r="L11" t="n">
         <v/>
@@ -69591,11 +69591,11 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Accuracy</t>
+          <t>Recall</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
         <v>0.7292</v>
@@ -69610,13 +69610,13 @@
         <v>0.7292</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7385</v>
+        <v>0.7309</v>
       </c>
       <c r="J12" t="n">
         <v>0.7292</v>
       </c>
       <c r="K12" t="n">
-        <v>0.733</v>
+        <v>0.73</v>
       </c>
       <c r="L12" t="n">
         <v/>
@@ -69625,42 +69625,42 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TVAE</t>
+          <t>GaussianCopula</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Accuracy</t>
+          <t>Recall</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>3</v>
       </c>
       <c r="E13" t="n">
-        <v>0.6944</v>
+        <v>0.7292</v>
       </c>
       <c r="F13" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="G13" t="n">
-        <v>614</v>
+        <v>10000</v>
       </c>
       <c r="H13" t="n">
-        <v>0.6944</v>
+        <v>0.7292</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4823</v>
+        <v>0.7385</v>
       </c>
       <c r="J13" t="n">
-        <v>0.6944</v>
+        <v>0.7292</v>
       </c>
       <c r="K13" t="n">
-        <v>0.5692</v>
+        <v>0.733</v>
       </c>
       <c r="L13" t="n">
         <v/>
@@ -69669,12 +69669,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GaussianCopula</t>
+          <t>TVAE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>LogisticRegression</t>
+          <t>KNN</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -69683,28 +69683,28 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>0.7917</v>
+        <v>0.6944</v>
       </c>
       <c r="F14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G14" t="n">
         <v>614</v>
       </c>
       <c r="H14" t="n">
-        <v>0.7917</v>
+        <v>0.6944</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7856</v>
+        <v>0.4823</v>
       </c>
       <c r="J14" t="n">
-        <v>0.7917</v>
+        <v>0.6944</v>
       </c>
       <c r="K14" t="n">
-        <v>0.7871</v>
+        <v>0.5692</v>
       </c>
       <c r="L14" t="n">
         <v/>
@@ -69713,12 +69713,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GaussianCopula</t>
+          <t>TVAE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>KNN</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -69727,28 +69727,28 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8056</v>
+        <v>0.6944</v>
       </c>
       <c r="F15" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="G15" t="n">
-        <v>10000</v>
+        <v>614</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8056</v>
+        <v>0.6944</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8238</v>
+        <v>0.4823</v>
       </c>
       <c r="J15" t="n">
-        <v>0.8056</v>
+        <v>0.6944</v>
       </c>
       <c r="K15" t="n">
-        <v>0.7795</v>
+        <v>0.5692</v>
       </c>
       <c r="L15" t="n">
         <v/>
@@ -69757,12 +69757,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CTGAN</t>
+          <t>TVAE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SVM</t>
+          <t>KNN</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -69777,7 +69777,7 @@
         <v>0.6944</v>
       </c>
       <c r="F16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="G16" t="n">
         <v>614</v>
@@ -69801,12 +69801,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>GaussianCopula</t>
+          <t>CTGAN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DecisionTree</t>
+          <t>KNN</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -69818,25 +69818,25 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7342</v>
+        <v>0.6378</v>
       </c>
       <c r="F17" t="n">
         <v>50</v>
       </c>
       <c r="G17" t="n">
-        <v>10000</v>
+        <v>3070</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7292</v>
+        <v>0.6806</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7427</v>
+        <v>0.6359</v>
       </c>
       <c r="J17" t="n">
-        <v>0.7292</v>
+        <v>0.6806</v>
       </c>
       <c r="K17" t="n">
-        <v>0.7342</v>
+        <v>0.6378</v>
       </c>
       <c r="L17" t="n">
         <v/>
@@ -69859,28 +69859,28 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6378</v>
+        <v>0.6369</v>
       </c>
       <c r="F18" t="n">
         <v>50</v>
       </c>
       <c r="G18" t="n">
-        <v>3070</v>
+        <v>614</v>
       </c>
       <c r="H18" t="n">
-        <v>0.6806</v>
+        <v>0.6875</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6359</v>
+        <v>0.6414</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6806</v>
+        <v>0.6875</v>
       </c>
       <c r="K18" t="n">
-        <v>0.6378</v>
+        <v>0.6369</v>
       </c>
       <c r="L18" t="n">
         <v/>
@@ -69889,12 +69889,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>GaussianCopula</t>
+          <t>CTGAN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>LogisticRegression</t>
+          <t>KNN</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -69903,28 +69903,28 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7871</v>
+        <v>0.6276</v>
       </c>
       <c r="F19" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="G19" t="n">
-        <v>614</v>
+        <v>6140</v>
       </c>
       <c r="H19" t="n">
-        <v>0.7917</v>
+        <v>0.6667</v>
       </c>
       <c r="I19" t="n">
-        <v>0.7856</v>
+        <v>0.6202</v>
       </c>
       <c r="J19" t="n">
-        <v>0.7917</v>
+        <v>0.6667</v>
       </c>
       <c r="K19" t="n">
-        <v>0.7871</v>
+        <v>0.6276</v>
       </c>
       <c r="L19" t="n">
         <v/>
@@ -69933,42 +69933,42 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>GaussianCopula</t>
+          <t>CTGAN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>KNN</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>Precision</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8011</v>
+        <v>0.6414</v>
       </c>
       <c r="F20" t="n">
         <v>50</v>
       </c>
       <c r="G20" t="n">
-        <v>10000</v>
+        <v>614</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8194</v>
+        <v>0.6875</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8287</v>
+        <v>0.6414</v>
       </c>
       <c r="J20" t="n">
-        <v>0.8194</v>
+        <v>0.6875</v>
       </c>
       <c r="K20" t="n">
-        <v>0.8011</v>
+        <v>0.6369</v>
       </c>
       <c r="L20" t="n">
         <v/>
@@ -69982,37 +69982,37 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SVM</t>
+          <t>KNN</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>Precision</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5965</v>
+        <v>0.6369</v>
       </c>
       <c r="F21" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="G21" t="n">
-        <v>1842</v>
+        <v>614</v>
       </c>
       <c r="H21" t="n">
-        <v>0.7014</v>
+        <v>0.6944</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6913</v>
+        <v>0.6369</v>
       </c>
       <c r="J21" t="n">
-        <v>0.7014</v>
+        <v>0.6944</v>
       </c>
       <c r="K21" t="n">
-        <v>0.5965</v>
+        <v>0.5815</v>
       </c>
       <c r="L21" t="n">
         <v/>
@@ -70021,42 +70021,42 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>GaussianCopula</t>
+          <t>CTGAN</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>DecisionTree</t>
+          <t>KNN</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>Precision</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>0.733</v>
+        <v>0.6359</v>
       </c>
       <c r="F22" t="n">
         <v>50</v>
       </c>
       <c r="G22" t="n">
-        <v>10000</v>
+        <v>3070</v>
       </c>
       <c r="H22" t="n">
-        <v>0.7292</v>
+        <v>0.6806</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7385</v>
+        <v>0.6359</v>
       </c>
       <c r="J22" t="n">
-        <v>0.7292</v>
+        <v>0.6806</v>
       </c>
       <c r="K22" t="n">
-        <v>0.733</v>
+        <v>0.6378</v>
       </c>
       <c r="L22" t="n">
         <v/>
@@ -70065,7 +70065,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CTGAN</t>
+          <t>TVAE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -70075,32 +70075,32 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>Recall</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6369</v>
+        <v>0.6944</v>
       </c>
       <c r="F23" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="G23" t="n">
         <v>614</v>
       </c>
       <c r="H23" t="n">
-        <v>0.6875</v>
+        <v>0.6944</v>
       </c>
       <c r="I23" t="n">
-        <v>0.6414</v>
+        <v>0.4823</v>
       </c>
       <c r="J23" t="n">
-        <v>0.6875</v>
+        <v>0.6944</v>
       </c>
       <c r="K23" t="n">
-        <v>0.6369</v>
+        <v>0.5692</v>
       </c>
       <c r="L23" t="n">
         <v/>
@@ -70109,24 +70109,24 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>GaussianCopula</t>
+          <t>TVAE</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>LogisticRegression</t>
+          <t>KNN</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>Recall</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>0.7871</v>
+        <v>0.6944</v>
       </c>
       <c r="F24" t="n">
         <v>15</v>
@@ -70135,16 +70135,16 @@
         <v>614</v>
       </c>
       <c r="H24" t="n">
-        <v>0.7917</v>
+        <v>0.6944</v>
       </c>
       <c r="I24" t="n">
-        <v>0.7856</v>
+        <v>0.4823</v>
       </c>
       <c r="J24" t="n">
-        <v>0.7917</v>
+        <v>0.6944</v>
       </c>
       <c r="K24" t="n">
-        <v>0.7871</v>
+        <v>0.5692</v>
       </c>
       <c r="L24" t="n">
         <v/>
@@ -70153,42 +70153,42 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>GaussianCopula</t>
+          <t>TVAE</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>KNN</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>Recall</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>0.7886</v>
+        <v>0.6944</v>
       </c>
       <c r="F25" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="G25" t="n">
         <v>614</v>
       </c>
       <c r="H25" t="n">
-        <v>0.8056</v>
+        <v>0.6944</v>
       </c>
       <c r="I25" t="n">
-        <v>0.8058999999999999</v>
+        <v>0.4823</v>
       </c>
       <c r="J25" t="n">
-        <v>0.8056</v>
+        <v>0.6944</v>
       </c>
       <c r="K25" t="n">
-        <v>0.7886</v>
+        <v>0.5692</v>
       </c>
       <c r="L25" t="n">
         <v/>
@@ -70197,42 +70197,42 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CTGAN</t>
+          <t>GaussianCopula</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SVM</t>
+          <t>LogisticRegression</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>Accuracy</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>0.5859</v>
+        <v>0.7917</v>
       </c>
       <c r="F26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G26" t="n">
         <v>614</v>
       </c>
       <c r="H26" t="n">
-        <v>0.6667</v>
+        <v>0.7917</v>
       </c>
       <c r="I26" t="n">
-        <v>0.5736</v>
+        <v>0.7856</v>
       </c>
       <c r="J26" t="n">
-        <v>0.6667</v>
+        <v>0.7917</v>
       </c>
       <c r="K26" t="n">
-        <v>0.5859</v>
+        <v>0.7871</v>
       </c>
       <c r="L26" t="n">
         <v/>
@@ -70246,37 +70246,37 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>DecisionTree</t>
+          <t>LogisticRegression</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>Accuracy</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>0.73</v>
+        <v>0.7917</v>
       </c>
       <c r="F27" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="G27" t="n">
-        <v>10000</v>
+        <v>614</v>
       </c>
       <c r="H27" t="n">
-        <v>0.7292</v>
+        <v>0.7917</v>
       </c>
       <c r="I27" t="n">
-        <v>0.7309</v>
+        <v>0.7856</v>
       </c>
       <c r="J27" t="n">
-        <v>0.7292</v>
+        <v>0.7917</v>
       </c>
       <c r="K27" t="n">
-        <v>0.73</v>
+        <v>0.7871</v>
       </c>
       <c r="L27" t="n">
         <v/>
@@ -70285,42 +70285,42 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CTGAN</t>
+          <t>GaussianCopula</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>LogisticRegression</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>Accuracy</t>
         </is>
       </c>
       <c r="D28" t="n">
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>0.6276</v>
+        <v>0.7917</v>
       </c>
       <c r="F28" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="G28" t="n">
-        <v>6140</v>
+        <v>614</v>
       </c>
       <c r="H28" t="n">
-        <v>0.6667</v>
+        <v>0.7917</v>
       </c>
       <c r="I28" t="n">
-        <v>0.6202</v>
+        <v>0.7856</v>
       </c>
       <c r="J28" t="n">
-        <v>0.6667</v>
+        <v>0.7917</v>
       </c>
       <c r="K28" t="n">
-        <v>0.6276</v>
+        <v>0.7871</v>
       </c>
       <c r="L28" t="n">
         <v/>
@@ -70343,13 +70343,13 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E29" t="n">
         <v>0.7871</v>
       </c>
       <c r="F29" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G29" t="n">
         <v>614</v>
@@ -70378,7 +70378,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>LogisticRegression</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -70387,28 +70387,28 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>0.7795</v>
+        <v>0.7871</v>
       </c>
       <c r="F30" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="G30" t="n">
-        <v>10000</v>
+        <v>614</v>
       </c>
       <c r="H30" t="n">
-        <v>0.8056</v>
+        <v>0.7917</v>
       </c>
       <c r="I30" t="n">
-        <v>0.8238</v>
+        <v>0.7856</v>
       </c>
       <c r="J30" t="n">
-        <v>0.8056</v>
+        <v>0.7917</v>
       </c>
       <c r="K30" t="n">
-        <v>0.7795</v>
+        <v>0.7871</v>
       </c>
       <c r="L30" t="n">
         <v/>
@@ -70417,12 +70417,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CTGAN</t>
+          <t>GaussianCopula</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SVM</t>
+          <t>LogisticRegression</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -70434,25 +70434,25 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>0.5851</v>
+        <v>0.7871</v>
       </c>
       <c r="F31" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="G31" t="n">
         <v>614</v>
       </c>
       <c r="H31" t="n">
-        <v>0.7014</v>
+        <v>0.7917</v>
       </c>
       <c r="I31" t="n">
-        <v>0.7912</v>
+        <v>0.7856</v>
       </c>
       <c r="J31" t="n">
-        <v>0.7014</v>
+        <v>0.7917</v>
       </c>
       <c r="K31" t="n">
-        <v>0.5851</v>
+        <v>0.7871</v>
       </c>
       <c r="L31" t="n">
         <v/>
@@ -70461,12 +70461,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>GaussianCopula</t>
+          <t>TVAE</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>DecisionTree</t>
+          <t>LogisticRegression</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -70478,25 +70478,25 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>0.7427</v>
+        <v>0.7912</v>
       </c>
       <c r="F32" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="G32" t="n">
-        <v>10000</v>
+        <v>614</v>
       </c>
       <c r="H32" t="n">
-        <v>0.7292</v>
+        <v>0.7014</v>
       </c>
       <c r="I32" t="n">
-        <v>0.7427</v>
+        <v>0.7912</v>
       </c>
       <c r="J32" t="n">
-        <v>0.7292</v>
+        <v>0.7014</v>
       </c>
       <c r="K32" t="n">
-        <v>0.7342</v>
+        <v>0.5851</v>
       </c>
       <c r="L32" t="n">
         <v/>
@@ -70510,7 +70510,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>LogisticRegression</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -70519,28 +70519,28 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>0.6414</v>
+        <v>0.7912</v>
       </c>
       <c r="F33" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="G33" t="n">
         <v>614</v>
       </c>
       <c r="H33" t="n">
-        <v>0.6875</v>
+        <v>0.7014</v>
       </c>
       <c r="I33" t="n">
-        <v>0.6414</v>
+        <v>0.7912</v>
       </c>
       <c r="J33" t="n">
-        <v>0.6875</v>
+        <v>0.7014</v>
       </c>
       <c r="K33" t="n">
-        <v>0.6369</v>
+        <v>0.5851</v>
       </c>
       <c r="L33" t="n">
         <v/>
@@ -70549,7 +70549,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>TVAE</t>
+          <t>GaussianCopula</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -70563,10 +70563,10 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>0.7912</v>
+        <v>0.7856</v>
       </c>
       <c r="F34" t="n">
         <v>10</v>
@@ -70575,16 +70575,16 @@
         <v>614</v>
       </c>
       <c r="H34" t="n">
-        <v>0.7014</v>
+        <v>0.7917</v>
       </c>
       <c r="I34" t="n">
-        <v>0.7912</v>
+        <v>0.7856</v>
       </c>
       <c r="J34" t="n">
-        <v>0.7014</v>
+        <v>0.7917</v>
       </c>
       <c r="K34" t="n">
-        <v>0.5851</v>
+        <v>0.7871</v>
       </c>
       <c r="L34" t="n">
         <v/>
@@ -70598,37 +70598,37 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>LogisticRegression</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Precision</t>
+          <t>Recall</t>
         </is>
       </c>
       <c r="D35" t="n">
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>0.8289</v>
+        <v>0.7917</v>
       </c>
       <c r="F35" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="G35" t="n">
         <v>614</v>
       </c>
       <c r="H35" t="n">
-        <v>0.7986</v>
+        <v>0.7917</v>
       </c>
       <c r="I35" t="n">
-        <v>0.8289</v>
+        <v>0.7856</v>
       </c>
       <c r="J35" t="n">
-        <v>0.7986</v>
+        <v>0.7917</v>
       </c>
       <c r="K35" t="n">
-        <v>0.766</v>
+        <v>0.7871</v>
       </c>
       <c r="L35" t="n">
         <v/>
@@ -70637,42 +70637,42 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CTGAN</t>
+          <t>GaussianCopula</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SVM</t>
+          <t>LogisticRegression</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Precision</t>
+          <t>Recall</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>0.7912</v>
+        <v>0.7917</v>
       </c>
       <c r="F36" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="G36" t="n">
         <v>614</v>
       </c>
       <c r="H36" t="n">
-        <v>0.7014</v>
+        <v>0.7917</v>
       </c>
       <c r="I36" t="n">
-        <v>0.7912</v>
+        <v>0.7856</v>
       </c>
       <c r="J36" t="n">
-        <v>0.7014</v>
+        <v>0.7917</v>
       </c>
       <c r="K36" t="n">
-        <v>0.5851</v>
+        <v>0.7871</v>
       </c>
       <c r="L36" t="n">
         <v/>
@@ -70686,37 +70686,37 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>DecisionTree</t>
+          <t>LogisticRegression</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Precision</t>
+          <t>Recall</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>0.7385</v>
+        <v>0.7917</v>
       </c>
       <c r="F37" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="G37" t="n">
-        <v>10000</v>
+        <v>614</v>
       </c>
       <c r="H37" t="n">
-        <v>0.7292</v>
+        <v>0.7917</v>
       </c>
       <c r="I37" t="n">
-        <v>0.7385</v>
+        <v>0.7856</v>
       </c>
       <c r="J37" t="n">
-        <v>0.7292</v>
+        <v>0.7917</v>
       </c>
       <c r="K37" t="n">
-        <v>0.733</v>
+        <v>0.7871</v>
       </c>
       <c r="L37" t="n">
         <v/>
@@ -70725,42 +70725,42 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CTGAN</t>
+          <t>GaussianCopula</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Precision</t>
+          <t>Accuracy</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>0.6369</v>
+        <v>0.8194</v>
       </c>
       <c r="F38" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="G38" t="n">
-        <v>614</v>
+        <v>10000</v>
       </c>
       <c r="H38" t="n">
-        <v>0.6944</v>
+        <v>0.8194</v>
       </c>
       <c r="I38" t="n">
-        <v>0.6369</v>
+        <v>0.8287</v>
       </c>
       <c r="J38" t="n">
-        <v>0.6944</v>
+        <v>0.8194</v>
       </c>
       <c r="K38" t="n">
-        <v>0.5815</v>
+        <v>0.8011</v>
       </c>
       <c r="L38" t="n">
         <v/>
@@ -70769,42 +70769,42 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>CTGAN</t>
+          <t>GaussianCopula</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>LogisticRegression</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Precision</t>
+          <t>Accuracy</t>
         </is>
       </c>
       <c r="D39" t="n">
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>0.7912</v>
+        <v>0.8056</v>
       </c>
       <c r="F39" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="G39" t="n">
         <v>614</v>
       </c>
       <c r="H39" t="n">
-        <v>0.7014</v>
+        <v>0.8056</v>
       </c>
       <c r="I39" t="n">
-        <v>0.7912</v>
+        <v>0.8058999999999999</v>
       </c>
       <c r="J39" t="n">
-        <v>0.7014</v>
+        <v>0.8056</v>
       </c>
       <c r="K39" t="n">
-        <v>0.5851</v>
+        <v>0.7886</v>
       </c>
       <c r="L39" t="n">
         <v/>
@@ -70823,14 +70823,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Precision</t>
+          <t>Accuracy</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>0.8287</v>
+        <v>0.8056</v>
       </c>
       <c r="F40" t="n">
         <v>50</v>
@@ -70839,16 +70839,16 @@
         <v>10000</v>
       </c>
       <c r="H40" t="n">
-        <v>0.8194</v>
+        <v>0.8056</v>
       </c>
       <c r="I40" t="n">
-        <v>0.8287</v>
+        <v>0.8238</v>
       </c>
       <c r="J40" t="n">
-        <v>0.8194</v>
+        <v>0.8056</v>
       </c>
       <c r="K40" t="n">
-        <v>0.8011</v>
+        <v>0.7795</v>
       </c>
       <c r="L40" t="n">
         <v/>
@@ -70857,42 +70857,42 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CTGAN</t>
+          <t>GaussianCopula</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SVM</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Precision</t>
+          <t>F1</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>0.6913</v>
+        <v>0.8011</v>
       </c>
       <c r="F41" t="n">
         <v>50</v>
       </c>
       <c r="G41" t="n">
-        <v>1842</v>
+        <v>10000</v>
       </c>
       <c r="H41" t="n">
-        <v>0.7014</v>
+        <v>0.8194</v>
       </c>
       <c r="I41" t="n">
-        <v>0.6913</v>
+        <v>0.8287</v>
       </c>
       <c r="J41" t="n">
-        <v>0.7014</v>
+        <v>0.8194</v>
       </c>
       <c r="K41" t="n">
-        <v>0.5965</v>
+        <v>0.8011</v>
       </c>
       <c r="L41" t="n">
         <v/>
@@ -70906,37 +70906,37 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>DecisionTree</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Precision</t>
+          <t>F1</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>0.7309</v>
+        <v>0.7886</v>
       </c>
       <c r="F42" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="G42" t="n">
-        <v>10000</v>
+        <v>614</v>
       </c>
       <c r="H42" t="n">
-        <v>0.7292</v>
+        <v>0.8056</v>
       </c>
       <c r="I42" t="n">
-        <v>0.7309</v>
+        <v>0.8058999999999999</v>
       </c>
       <c r="J42" t="n">
-        <v>0.7292</v>
+        <v>0.8056</v>
       </c>
       <c r="K42" t="n">
-        <v>0.73</v>
+        <v>0.7886</v>
       </c>
       <c r="L42" t="n">
         <v/>
@@ -70945,42 +70945,42 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CTGAN</t>
+          <t>GaussianCopula</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Precision</t>
+          <t>F1</t>
         </is>
       </c>
       <c r="D43" t="n">
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>0.6359</v>
+        <v>0.7795</v>
       </c>
       <c r="F43" t="n">
         <v>50</v>
       </c>
       <c r="G43" t="n">
-        <v>3070</v>
+        <v>10000</v>
       </c>
       <c r="H43" t="n">
-        <v>0.6806</v>
+        <v>0.8056</v>
       </c>
       <c r="I43" t="n">
-        <v>0.6359</v>
+        <v>0.8238</v>
       </c>
       <c r="J43" t="n">
-        <v>0.6806</v>
+        <v>0.8056</v>
       </c>
       <c r="K43" t="n">
-        <v>0.6378</v>
+        <v>0.7795</v>
       </c>
       <c r="L43" t="n">
         <v/>
@@ -70994,7 +70994,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>LogisticRegression</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -71003,28 +71003,28 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>0.7856</v>
+        <v>0.8289</v>
       </c>
       <c r="F44" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="G44" t="n">
         <v>614</v>
       </c>
       <c r="H44" t="n">
-        <v>0.7917</v>
+        <v>0.7986</v>
       </c>
       <c r="I44" t="n">
-        <v>0.7856</v>
+        <v>0.8289</v>
       </c>
       <c r="J44" t="n">
-        <v>0.7917</v>
+        <v>0.7986</v>
       </c>
       <c r="K44" t="n">
-        <v>0.7871</v>
+        <v>0.766</v>
       </c>
       <c r="L44" t="n">
         <v/>
@@ -71047,10 +71047,10 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>0.8238</v>
+        <v>0.8287</v>
       </c>
       <c r="F45" t="n">
         <v>50</v>
@@ -71059,16 +71059,16 @@
         <v>10000</v>
       </c>
       <c r="H45" t="n">
-        <v>0.8056</v>
+        <v>0.8194</v>
       </c>
       <c r="I45" t="n">
-        <v>0.8238</v>
+        <v>0.8287</v>
       </c>
       <c r="J45" t="n">
-        <v>0.8056</v>
+        <v>0.8194</v>
       </c>
       <c r="K45" t="n">
-        <v>0.7795</v>
+        <v>0.8011</v>
       </c>
       <c r="L45" t="n">
         <v/>
@@ -71077,12 +71077,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>CTGAN</t>
+          <t>GaussianCopula</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SVM</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -71094,25 +71094,25 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>0.6369</v>
+        <v>0.8238</v>
       </c>
       <c r="F46" t="n">
         <v>50</v>
       </c>
       <c r="G46" t="n">
-        <v>6140</v>
+        <v>10000</v>
       </c>
       <c r="H46" t="n">
-        <v>0.6944</v>
+        <v>0.8056</v>
       </c>
       <c r="I46" t="n">
-        <v>0.6369</v>
+        <v>0.8238</v>
       </c>
       <c r="J46" t="n">
-        <v>0.6944</v>
+        <v>0.8056</v>
       </c>
       <c r="K46" t="n">
-        <v>0.5815</v>
+        <v>0.7795</v>
       </c>
       <c r="L46" t="n">
         <v/>
@@ -71126,7 +71126,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>DecisionTree</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -71138,7 +71138,7 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>0.7292</v>
+        <v>0.8194</v>
       </c>
       <c r="F47" t="n">
         <v>50</v>
@@ -71147,16 +71147,16 @@
         <v>10000</v>
       </c>
       <c r="H47" t="n">
-        <v>0.7292</v>
+        <v>0.8194</v>
       </c>
       <c r="I47" t="n">
-        <v>0.7427</v>
+        <v>0.8287</v>
       </c>
       <c r="J47" t="n">
-        <v>0.7292</v>
+        <v>0.8194</v>
       </c>
       <c r="K47" t="n">
-        <v>0.7342</v>
+        <v>0.8011</v>
       </c>
       <c r="L47" t="n">
         <v/>
@@ -71165,12 +71165,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>TVAE</t>
+          <t>GaussianCopula</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -71179,10 +71179,10 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>0.6944</v>
+        <v>0.8056</v>
       </c>
       <c r="F48" t="n">
         <v>10</v>
@@ -71191,16 +71191,16 @@
         <v>614</v>
       </c>
       <c r="H48" t="n">
-        <v>0.6944</v>
+        <v>0.8056</v>
       </c>
       <c r="I48" t="n">
-        <v>0.4823</v>
+        <v>0.8058999999999999</v>
       </c>
       <c r="J48" t="n">
-        <v>0.6944</v>
+        <v>0.8056</v>
       </c>
       <c r="K48" t="n">
-        <v>0.5692</v>
+        <v>0.7886</v>
       </c>
       <c r="L48" t="n">
         <v/>
@@ -71214,7 +71214,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>LogisticRegression</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -71223,28 +71223,28 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>0.7917</v>
+        <v>0.8056</v>
       </c>
       <c r="F49" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="G49" t="n">
-        <v>614</v>
+        <v>10000</v>
       </c>
       <c r="H49" t="n">
-        <v>0.7917</v>
+        <v>0.8056</v>
       </c>
       <c r="I49" t="n">
-        <v>0.7856</v>
+        <v>0.8238</v>
       </c>
       <c r="J49" t="n">
-        <v>0.7917</v>
+        <v>0.8056</v>
       </c>
       <c r="K49" t="n">
-        <v>0.7871</v>
+        <v>0.7795</v>
       </c>
       <c r="L49" t="n">
         <v/>
@@ -71253,42 +71253,42 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>GaussianCopula</t>
+          <t>CTGAN</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>SVM</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Recall</t>
+          <t>Accuracy</t>
         </is>
       </c>
       <c r="D50" t="n">
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>0.8194</v>
+        <v>0.7014</v>
       </c>
       <c r="F50" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="G50" t="n">
-        <v>10000</v>
+        <v>614</v>
       </c>
       <c r="H50" t="n">
-        <v>0.8194</v>
+        <v>0.7014</v>
       </c>
       <c r="I50" t="n">
-        <v>0.8287</v>
+        <v>0.7912</v>
       </c>
       <c r="J50" t="n">
-        <v>0.8194</v>
+        <v>0.7014</v>
       </c>
       <c r="K50" t="n">
-        <v>0.8011</v>
+        <v>0.5851</v>
       </c>
       <c r="L50" t="n">
         <v/>
@@ -71307,32 +71307,32 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Recall</t>
+          <t>Accuracy</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E51" t="n">
         <v>0.7014</v>
       </c>
       <c r="F51" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="G51" t="n">
-        <v>614</v>
+        <v>1842</v>
       </c>
       <c r="H51" t="n">
         <v>0.7014</v>
       </c>
       <c r="I51" t="n">
-        <v>0.7912</v>
+        <v>0.6913</v>
       </c>
       <c r="J51" t="n">
         <v>0.7014</v>
       </c>
       <c r="K51" t="n">
-        <v>0.5851</v>
+        <v>0.5965</v>
       </c>
       <c r="L51" t="n">
         <v/>
@@ -71341,42 +71341,42 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>GaussianCopula</t>
+          <t>CTGAN</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>DecisionTree</t>
+          <t>SVM</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Recall</t>
+          <t>Accuracy</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>0.7292</v>
+        <v>0.6944</v>
       </c>
       <c r="F52" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="G52" t="n">
-        <v>10000</v>
+        <v>614</v>
       </c>
       <c r="H52" t="n">
-        <v>0.7292</v>
+        <v>0.6944</v>
       </c>
       <c r="I52" t="n">
-        <v>0.7309</v>
+        <v>0.4823</v>
       </c>
       <c r="J52" t="n">
-        <v>0.7292</v>
+        <v>0.6944</v>
       </c>
       <c r="K52" t="n">
-        <v>0.73</v>
+        <v>0.5692</v>
       </c>
       <c r="L52" t="n">
         <v/>
@@ -71385,42 +71385,42 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>TVAE</t>
+          <t>CTGAN</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>SVM</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Recall</t>
+          <t>F1</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>0.6944</v>
+        <v>0.5965</v>
       </c>
       <c r="F53" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="G53" t="n">
-        <v>614</v>
+        <v>1842</v>
       </c>
       <c r="H53" t="n">
-        <v>0.6944</v>
+        <v>0.7014</v>
       </c>
       <c r="I53" t="n">
-        <v>0.4823</v>
+        <v>0.6913</v>
       </c>
       <c r="J53" t="n">
-        <v>0.6944</v>
+        <v>0.7014</v>
       </c>
       <c r="K53" t="n">
-        <v>0.5692</v>
+        <v>0.5965</v>
       </c>
       <c r="L53" t="n">
         <v/>
@@ -71429,42 +71429,42 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>GaussianCopula</t>
+          <t>CTGAN</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>LogisticRegression</t>
+          <t>SVM</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Recall</t>
+          <t>F1</t>
         </is>
       </c>
       <c r="D54" t="n">
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>0.7917</v>
+        <v>0.5859</v>
       </c>
       <c r="F54" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="G54" t="n">
         <v>614</v>
       </c>
       <c r="H54" t="n">
-        <v>0.7917</v>
+        <v>0.6667</v>
       </c>
       <c r="I54" t="n">
-        <v>0.7856</v>
+        <v>0.5736</v>
       </c>
       <c r="J54" t="n">
-        <v>0.7917</v>
+        <v>0.6667</v>
       </c>
       <c r="K54" t="n">
-        <v>0.7871</v>
+        <v>0.5859</v>
       </c>
       <c r="L54" t="n">
         <v/>
@@ -71473,42 +71473,42 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>GaussianCopula</t>
+          <t>CTGAN</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>SVM</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Recall</t>
+          <t>F1</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>0.8056</v>
+        <v>0.5851</v>
       </c>
       <c r="F55" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="G55" t="n">
         <v>614</v>
       </c>
       <c r="H55" t="n">
-        <v>0.8056</v>
+        <v>0.7014</v>
       </c>
       <c r="I55" t="n">
-        <v>0.8058999999999999</v>
+        <v>0.7912</v>
       </c>
       <c r="J55" t="n">
-        <v>0.8056</v>
+        <v>0.7014</v>
       </c>
       <c r="K55" t="n">
-        <v>0.7886</v>
+        <v>0.5851</v>
       </c>
       <c r="L55" t="n">
         <v/>
@@ -71527,32 +71527,32 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Recall</t>
+          <t>Precision</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>0.7014</v>
+        <v>0.7912</v>
       </c>
       <c r="F56" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="G56" t="n">
-        <v>1842</v>
+        <v>614</v>
       </c>
       <c r="H56" t="n">
         <v>0.7014</v>
       </c>
       <c r="I56" t="n">
-        <v>0.6913</v>
+        <v>0.7912</v>
       </c>
       <c r="J56" t="n">
         <v>0.7014</v>
       </c>
       <c r="K56" t="n">
-        <v>0.5965</v>
+        <v>0.5851</v>
       </c>
       <c r="L56" t="n">
         <v/>
@@ -71561,42 +71561,42 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>GaussianCopula</t>
+          <t>CTGAN</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>DecisionTree</t>
+          <t>SVM</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Recall</t>
+          <t>Precision</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>0.7292</v>
+        <v>0.6913</v>
       </c>
       <c r="F57" t="n">
         <v>50</v>
       </c>
       <c r="G57" t="n">
-        <v>10000</v>
+        <v>1842</v>
       </c>
       <c r="H57" t="n">
-        <v>0.7292</v>
+        <v>0.7014</v>
       </c>
       <c r="I57" t="n">
-        <v>0.7385</v>
+        <v>0.6913</v>
       </c>
       <c r="J57" t="n">
-        <v>0.7292</v>
+        <v>0.7014</v>
       </c>
       <c r="K57" t="n">
-        <v>0.733</v>
+        <v>0.5965</v>
       </c>
       <c r="L57" t="n">
         <v/>
@@ -71605,42 +71605,42 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>TVAE</t>
+          <t>CTGAN</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>SVM</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Recall</t>
+          <t>Precision</t>
         </is>
       </c>
       <c r="D58" t="n">
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>0.6944</v>
+        <v>0.6369</v>
       </c>
       <c r="F58" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="G58" t="n">
-        <v>614</v>
+        <v>6140</v>
       </c>
       <c r="H58" t="n">
         <v>0.6944</v>
       </c>
       <c r="I58" t="n">
-        <v>0.4823</v>
+        <v>0.6369</v>
       </c>
       <c r="J58" t="n">
         <v>0.6944</v>
       </c>
       <c r="K58" t="n">
-        <v>0.5692</v>
+        <v>0.5815</v>
       </c>
       <c r="L58" t="n">
         <v/>
@@ -71649,12 +71649,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>GaussianCopula</t>
+          <t>CTGAN</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>LogisticRegression</t>
+          <t>SVM</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -71663,28 +71663,28 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>0.7917</v>
+        <v>0.7014</v>
       </c>
       <c r="F59" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G59" t="n">
         <v>614</v>
       </c>
       <c r="H59" t="n">
-        <v>0.7917</v>
+        <v>0.7014</v>
       </c>
       <c r="I59" t="n">
-        <v>0.7856</v>
+        <v>0.7912</v>
       </c>
       <c r="J59" t="n">
-        <v>0.7917</v>
+        <v>0.7014</v>
       </c>
       <c r="K59" t="n">
-        <v>0.7871</v>
+        <v>0.5851</v>
       </c>
       <c r="L59" t="n">
         <v/>
@@ -71693,12 +71693,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>GaussianCopula</t>
+          <t>CTGAN</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>SVM</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -71707,28 +71707,28 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>0.8056</v>
+        <v>0.7014</v>
       </c>
       <c r="F60" t="n">
         <v>50</v>
       </c>
       <c r="G60" t="n">
-        <v>10000</v>
+        <v>1842</v>
       </c>
       <c r="H60" t="n">
-        <v>0.8056</v>
+        <v>0.7014</v>
       </c>
       <c r="I60" t="n">
-        <v>0.8238</v>
+        <v>0.6913</v>
       </c>
       <c r="J60" t="n">
-        <v>0.8056</v>
+        <v>0.7014</v>
       </c>
       <c r="K60" t="n">
-        <v>0.7795</v>
+        <v>0.5965</v>
       </c>
       <c r="L60" t="n">
         <v/>

--- a/outputs/batch/loan_batch_2025-04-11_14-27-40/batch_analysis/combined_results.xlsx
+++ b/outputs/batch/loan_batch_2025-04-11_14-27-40/batch_analysis/combined_results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ac15ec0ad8aeca88/Documents/Desktop/Master_Thesis/MasterThesisCode/outputs/batch/loan_batch_2025-04-11_14-27-40/batch_analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_D1B55B6EFC93996906754F48B4DED98C0601DB6A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_D1B55B6EFC93996906754F244C5CEAA00601DB6A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8B6030EE-57F7-483B-8FB9-13FFAE46A066}"/>
   <bookViews>
-    <workbookView xWindow="32040" yWindow="-10530" windowWidth="21600" windowHeight="11295" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="33060" yWindow="-4605" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="combined_results" sheetId="1" r:id="rId1"/>
@@ -60219,8 +60219,8 @@
   <dimension ref="A1:L61"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13" customWidth="1"/>
     <col min="4" max="4" width="6" customWidth="1"/>
     <col min="5" max="5" width="13" customWidth="1"/>
